--- a/exports/attributes_v2.xlsx
+++ b/exports/attributes_v2.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Attributes v2'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Attributes v2'!$A$1:$I$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dict formats'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Old -&gt; New mapping'!$A$1:$F$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Old -&gt; New mapping'!$A$1:$F$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JSON schema'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -90,10 +85,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -464,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="130" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -491,7 +483,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Attributes v2 - a PROPOSAL for Siva to approve BEFORE any DB migration. Nothing here is in the DB yet; the 8 NEW list attributes are proposed additions.</t>
+          <t>Attributes v2 - a PROPOSAL for Siva to approve BEFORE any DB migration. Version 2 (rev 2). Nothing here is in the DB yet; the 7 NEW list attributes are proposed additions.</t>
         </is>
       </c>
     </row>
@@ -503,139 +495,103 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The attributes of 9 groups (Assets, Banking / Accounts, Expenses, Goals, Income, Insurance, Liabilities, Tax, Tax / Compliance) are replaced by ONE list-of-dicts attribute per group (8 new attributes - Tax and Tax / Compliance merge into tax_items). Every other attribute stays exactly as it is in the DB. Group 'Banking' (credit_cards, basic_info agent) and every other group are NOT replaced.</t>
+          <t>The attributes of 7 groups (Assets, Banking / Accounts, Expenses, Goals, Income, Insurance, Liabilities) are replaced by ONE list attribute per group (7 new attributes). Every other attribute stays exactly as it is in the DB - including groups 'Tax' and 'Tax / Compliance' (Tax reverted, v1 attributes kept separate), group 'Banking' (credit_cards, basic_info agent) and every other group.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>New attributes (8)</t>
+          <t>New attributes (7)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>assets (Assets, agent asset); accounts (Banking / Accounts, agent account); expenses (Expenses, agent expense); goals (Goals, agent goal); income_sources (Income, agent income); insurance_policies (Insurance, agent tax_and_insurance); liabilities (Liabilities, agent liability); tax_items (Tax, agent tax_and_insurance). All new attributes: type array, array_items kind object.</t>
+          <t>assets (Assets, agent asset); accounts (Banking / Accounts, agent account); expenses (Expenses, agent expense); goals (Goals, agent goal); income_sources (Income, agent income); insurance_policies (Insurance, agent tax_and_insurance); liabilities (Liabilities, agent liability). All new attributes: type array, array_items kind object.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Amount convention</t>
+          <t>Result contract (no outer wrapper for NEW lists)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Every field whose name ends in amount or is called balance: type string, nullable. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+          <t>For the 7 NEW list attributes the result contract wrapper {value, confidence, confidence_type, evidence} is NOT used - the attribute value IS the list, and confidence / confidence_type / evidence live only on each item. All UNCHANGED attributes keep the wrapper.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Common fields (added LAST to every item)</t>
+          <t>Amount convention</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>confidence: number 0-1, required. How confident the model is in this item (0-1). | confidence_type: enum [quoted | normalized | inferred | calculated | not_found], required. quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. | evidence: string, nullable. Short verbatim quote(s) from the transcript supporting this item.</t>
+          <t>Every field whose name ends in amount or is called balance: type string, nullable. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Item-level rule</t>
+          <t>Common fields (per ITEM, added LAST to every item)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Appended to each new attribute's description: Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>confidence: number 0-1, required. How confident the model is in this item (0-1). | confidence_type: enum [quoted | normalized | inferred | calculated | not_found], required. quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. | evidence: string, nullable. Short verbatim quote(s) from the transcript supporting this item.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OPEN DECISION 1</t>
+          <t>Item-level rule</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Insurance has two boolean judgements (term_insurance_coverage_adequacy, health_insurance_coverage_adequacy) that are not list items - proposed to KEEP them unchanged next to insurance_policies; delete only if Siva confirms.</t>
+          <t>Appended to each new attribute's definition: Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>OPEN DECISION 2</t>
+          <t>Decisions (approved by Siva, 2026-10-03)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Every attribute is already wrapped by the result contract {value, confidence, confidence_type, evidence}. With per-item confidence the wrapper on these 8 list attributes becomes a group-level summary - proposed: keep the wrapper (overall confidence; evidence may be null).</t>
+          <t>(1) Insurance adequacy booleans (term_insurance_coverage_adequacy, health_insurance_coverage_adequacy) are KEPT as-is. (2) All proposed extra item fields (name, provider, account_name, location, description, frequency, priority, insurer, policy_name, covered_members, premium_*, source, lender, emi_amount, interest_rate, end_year) are ACCEPTED. (3) Tax REVERTED - groups 'Tax' and 'Tax / Compliance' keep their current (v1) separate attributes; there is no tax_items attribute. (4) NO outer confidence wrapper for the 7 NEW list attributes - the value IS the list, confidence lives only on items; unchanged attributes keep the wrapper. (5) confidence_type uses all five values (quoted, normalized, inferred, calculated, not_found) - note the current extraction schema enum is missing 'calculated'.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OPEN DECISION 3</t>
+          <t>Counts</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Group 'Tax / Compliance' (gst_services, w8_ben) is merged into tax_items under group 'Tax'; Auto Select routing (groups 'Tax' + 'Tax / Compliance') keeps working.</t>
+          <t>Attributes in DB now: 118. Attributes deleted by this proposal: 77 (every attribute in the 7 groups except the 2 adequacy booleans, which are kept). Attributes after (proposed catalogue): 48 (41 unchanged incl. 2 kept adequacy booleans + 7 NEW).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>OPEN DECISION 4</t>
+          <t>Sheets</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fields beyond Siva's minimum (name, provider, account_name, location, description, frequency, priority, insurer, policy_name, covered_members, premium_*, source, lender, emi_amount, interest_rate, end_year, country, years, summary) are proposals - remove any not wanted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OPEN DECISION 5</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>The current extraction schema enum for confidence_type is [quoted, inferred, normalized, not_found] while the prompt also documents 'calculated'; v2 uses all five values for both the wrapper and items.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Attributes in DB now: 118. Attributes deleted by this proposal: 85 (every attribute in the 9 groups except the 2 adequacy booleans). Attributes after (proposed catalogue): 41 (33 unchanged incl. 2 KEEP? + 8 NEW).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Attributes v2 = full proposed catalogue sorted by Group then Name. Dict formats = one block per new attribute with field table + JSON example. Old -&gt; New mapping = one row per deleted attribute + 2 KEEP? rows. JSON schema = strict OpenRouter json_schema fragment per new attribute.</t>
+          <t>Attributes v2 = full proposed catalogue sorted by Group then Name. Dict formats = one block per new attribute with field table + 3 JSON examples. Old -&gt; New mapping = one row per deleted attribute + 2 kept-as-is rows. JSON schema = strict OpenRouter json_schema fragment per new attribute.</t>
         </is>
       </c>
     </row>
@@ -651,14 +607,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -712,7 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="420" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -735,7 +691,67 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all asset holdings. Each item is one holding/instance with its type, name, location and value. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every asset holding the Client mentions into a single list so the planner sees the full portfolio in one place. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- asset_type (enum, required): Type of asset holding, e.g. 'stocks', 'bonds', 'real_estate'. Allowed values: stocks, unlisted_stocks, equity_mutual_fund, equity_etf, commodity_etf, debt_etf, deposit, cash, debt_mf, personal_debt, bonds, reits, real_estate, crypto, others, total. Meanings: unlisted_stocks = shares not listed on an exchange (e.g. ESOPs, startup equity); deposit = fixed/recurring deposits held outside bank accounts listed in accounts; personal_debt = money the Client has lent to someone; others = any type not listed; total = an explicitly stated total for the group.
+- name (string, nullable): Instrument / scheme / property / borrower name, e.g. 'HDFC Flexi Cap', 'Flat in Whitefield, Bengaluru'.
+- location (enum, nullable): Where the asset is held, e.g. 'India'. For asset_type total, null = overall total across locations. Allowed values: India, Foreign.
+- amount (string, nullable): Current value, or units held, e.g. 'INR 500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "I have about 5 lakh in RBI bonds and around 2 lakh in HDFC Flexi Cap." -&gt; [
+  {
+    "asset_type": "bonds",
+    "name": "RBI bonds",
+    "location": "India",
+    "amount": "INR 500000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I have about 5 lakh in RBI bonds"
+  },
+  {
+    "asset_type": "equity_mutual_fund",
+    "name": "HDFC Flexi Cap",
+    "location": "India",
+    "amount": "INR 200000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "around 2 lakh in HDFC Flexi Cap"
+  }
+]
+Example 2 - Client: "I hold about $5,400 of Apple shares in my US brokerage." -&gt; [
+  {
+    "asset_type": "stocks",
+    "name": "Apple shares",
+    "location": "Foreign",
+    "amount": "USD 5400",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I hold about $5,400 of Apple shares in my US brokerage"
+  }
+]
+Example 3 - Client: "I do hold some crypto but I don't track the value, and I own no real estate." -&gt; [
+  {
+    "asset_type": "crypto",
+    "name": null,
+    "location": null,
+    "amount": "Yes",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I do hold some crypto but I don't track the value"
+  },
+  {
+    "asset_type": "real_estate",
+    "name": null,
+    "location": null,
+    "amount": "0",
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I own no real estate"
+  }
+]</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -796,7 +812,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="120" customHeight="1">
+    <row r="4" ht="420" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -819,7 +835,73 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all accounts (bank, investment, government schemes, brokers, custody). Each item is one account with its type, provider, name, location and balance. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every account the Client mentions - bank, investment, government schemes, brokers and custody - into a single list so balances can be totalled per location. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- account_type (enum, required): Type of account, e.g. 'bank_account', 'ppf'. Allowed values: investment_account, bank_account, ppf, bank_deposit, nps, ssy, epf, pms, aif, crypto_broker, self_custody, others. Meanings: ppf = Public Provident Fund; bank_deposit = fixed/recurring deposit held at a bank; nps = National Pension System; ssy = Sukanya Samriddhi Yojana; epf = Employees' Provident Fund; pms = Portfolio Management Service; aif = Alternative Investment Fund; crypto_broker = exchange or broker account for crypto; self_custody = crypto held in the Client's own wallet; others = any type not listed.
+- provider (string, nullable): Bank / broker / fund house / wallet name, e.g. 'HDFC Bank', 'Zerodha'.
+- account_name (string, nullable): Specific account or product name if given, e.g. 'Salary account'.
+- location (enum, nullable): Where the account is held, e.g. 'India'. Allowed values: India, Foreign.
+- balance (string, nullable): Account balance, e.g. 'INR 250000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "I have around 2.5 lakh in my HDFC salary account and about 8 lakh in PPF." -&gt; [
+  {
+    "account_type": "bank_account",
+    "provider": "HDFC Bank",
+    "account_name": "Salary account",
+    "location": "India",
+    "balance": "INR 250000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "around 2.5 lakh in my HDFC salary account"
+  },
+  {
+    "account_type": "ppf",
+    "provider": null,
+    "account_name": null,
+    "location": "India",
+    "balance": "INR 800000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about 8 lakh in PPF"
+  }
+]
+Example 2 - Client: "I keep about ten thousand dollars in my Chase savings account in the US." -&gt; [
+  {
+    "account_type": "bank_account",
+    "provider": "Chase",
+    "account_name": "Savings account",
+    "location": "Foreign",
+    "balance": "USD 10000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about ten thousand dollars in my Chase savings account in the US"
+  }
+]
+Example 3 - Client: "I do have an NPS account but I don't remember the balance, and I have no crypto account." -&gt; [
+  {
+    "account_type": "nps",
+    "provider": null,
+    "account_name": null,
+    "location": "India",
+    "balance": "Yes",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I do have an NPS account but I don't remember the balance"
+  },
+  {
+    "account_type": "crypto_broker",
+    "provider": null,
+    "account_name": null,
+    "location": null,
+    "balance": "0",
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I have no crypto account"
+  }
+]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
@@ -1524,7 +1606,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="120" customHeight="1">
+    <row r="22" ht="420" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1547,7 +1629,67 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all recurring and one-time expenses. Each item is one expense type with amount and frequency. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every expense the Client mentions, recurring or one-time, into a single list so the planner sees the full outflow picture. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- expense_type (enum, required): Type of expense, e.g. 'rent', 'travel_vacations'. Allowed values: rent, utilities, groceries, household_staff, childcare_school_fees, entertainment_dining, transport_fuel, family_support, shopping_purchases, subscriptions_memberships, insurance_premiums, travel_vacations, medical_expenses, loan_emis_education, loan_emis_personal, loan_emis_home, loan_emis_vehicle, loan_emis_others, loan_emis_total, charity_donations, miscellaneous, total. Meanings: loan_emis_* = EMI paid for that loan type; loan_emis_total = an explicitly stated total across EMIs; charity_donations = giving; miscellaneous = anything not listed; total = an explicitly stated total for the group.
+- description (string, nullable): What the expense is for, e.g. '2BHK in Whitefield, Bengaluru'.
+- amount (string, nullable): Amount per period, e.g. 'INR 30000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- frequency (enum, nullable): How often it recurs, e.g. 'monthly'. Keep the Client's own period - do NOT convert annual to monthly. Allowed values: monthly, annual, one_time.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "We pay 30k rent for our 2BHK in Whitefield and 5k for utilities every month." -&gt; [
+  {
+    "expense_type": "rent",
+    "description": "2BHK in Whitefield, Bengaluru",
+    "amount": "INR 30000",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "We pay 30k rent for our 2BHK in Whitefield"
+  },
+  {
+    "expense_type": "utilities",
+    "description": null,
+    "amount": "INR 5000",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "5k for utilities every month"
+  }
+]
+Example 2 - Client: "We spend about 2 lakh a year on travel and vacations." -&gt; [
+  {
+    "expense_type": "travel_vacations",
+    "description": null,
+    "amount": "INR 200000",
+    "frequency": "annual",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about 2 lakh a year on travel and vacations"
+  }
+]
+Example 3 - Client: "Groceries I don't track exactly, and we pay zero rent since we own the house." -&gt; [
+  {
+    "expense_type": "groceries",
+    "description": null,
+    "amount": "Yes",
+    "frequency": null,
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "Groceries I don't track exactly"
+  },
+  {
+    "expense_type": "rent",
+    "description": "Own house, no rent",
+    "amount": "0",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "inferred",
+    "evidence": "we pay zero rent since we own the house"
+  }
+]</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
@@ -1608,7 +1750,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="120" customHeight="1">
+    <row r="24" ht="420" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1631,7 +1773,63 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all client goals. Each item is one goal with type, description, target amount, target year and priority. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every goal the Client mentions into a single list so the planner can size, time and prioritise each one. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- goal_type (enum, required): Type of goal, e.g. 'buying_a_house_india', 'financial_freedom_fire'. Allowed values: planning_a_child, child_s_college_education, child_s_higher_education, buying_a_house_india, buying_a_vehicle, wedding_expenses, parents_healthcare_fund, vacation_travel_fund, legacy_inheritance, financial_freedom_fire, other_goals. Meanings: planning_a_child = expecting- or first-child costs; child_s_college_education / child_s_higher_education = UG / PG or study-abroad costs; buying_a_house_india = India home purchase; financial_freedom_fire = retire-early corpus; legacy_inheritance = leave-behind for heirs; other_goals = any goal not listed.
+- description (string, nullable): Goal in the Client's own terms, e.g. "Daughter's MS in the US".
+- target_amount (string, nullable): Target corpus / cost, e.g. 'INR 8000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- target_year (integer, nullable): Calendar year the Client wants to achieve the goal, e.g. 2032. If stated as 'in N years', add N to the meeting year and use confidence_type calculated.
+- priority (enum, nullable): How important the goal is, e.g. 'high'. Only when the Client indicates it. Allowed values: high, medium, low.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "We want around 80 lakh for our daughter's MS in the US by 2032, and about 1 crore for a house in India." -&gt; [
+  {
+    "goal_type": "child_s_higher_education",
+    "description": "Daughter's MS in the US",
+    "target_amount": "INR 8000000",
+    "target_year": 2032,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "around 80 lakh for our daughter's MS in the US by 2032"
+  },
+  {
+    "goal_type": "buying_a_house_india",
+    "description": "House in India",
+    "target_amount": "INR 10000000",
+    "target_year": null,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "about 1 crore for a house in India"
+  }
+]
+Example 2 - Client: "We want to retire in 15 years with a 5 crore corpus. (Meeting year 2026.)" -&gt; [
+  {
+    "goal_type": "financial_freedom_fire",
+    "description": "Retire with a 5 crore corpus",
+    "target_amount": "INR 50000000",
+    "target_year": 2041,
+    "priority": null,
+    "confidence": 0.8,
+    "confidence_type": "calculated",
+    "evidence": "retire in 15 years with a 5 crore corpus"
+  }
+]
+Example 3 - Client: "We are planning for a child but haven't fixed any amount yet." -&gt; [
+  {
+    "goal_type": "planning_a_child",
+    "description": "Planning for a child",
+    "target_amount": "Yes",
+    "target_year": null,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "quoted",
+    "evidence": "planning for a child but haven't fixed any amount yet"
+  }
+]</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -1740,7 +1938,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="120" customHeight="1">
+    <row r="27" ht="420" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1763,7 +1961,73 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all income sources. Each item is one source with type, source name, amount, frequency and location. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every income source the Client mentions into a single list so total inflow can be compared against expenses. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- income_type (enum, required): Type of income, e.g. 'salary', 'rental'. Allowed values: salary, business, capital_gains, rental, speculation, other_income. Meanings: capital_gains = profit from selling assets; rental = rent received; speculation = F&amp;O, intraday or lottery-type gains; other_income = any source not listed.
+- source (string, nullable): Employer / business / property name, e.g. 'Infosys', 'Pune flat rent'.
+- amount (string, nullable): Amount per period, e.g. 'INR 200000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- frequency (enum, nullable): Pay frequency, e.g. 'monthly'. Allowed values: monthly, annual, one_time.
+- location (enum, nullable): Where the income is earned, e.g. 'India'. Allowed values: India, Foreign.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "My monthly salary at Infosys is 2 lakh and we get 25k rent from our Pune flat." -&gt; [
+  {
+    "income_type": "salary",
+    "source": "Infosys",
+    "amount": "INR 200000",
+    "frequency": "monthly",
+    "location": "India",
+    "confidence": 0.95,
+    "confidence_type": "normalized",
+    "evidence": "My monthly salary at Infosys is 2 lakh"
+  },
+  {
+    "income_type": "rental",
+    "source": "Pune flat",
+    "amount": "INR 25000",
+    "frequency": "monthly",
+    "location": "India",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "we get 25k rent from our Pune flat"
+  }
+]
+Example 2 - Client: "I earn about $5,400 a month from my US contracting work." -&gt; [
+  {
+    "income_type": "salary",
+    "source": "US contracting work",
+    "amount": "USD 5400",
+    "frequency": "monthly",
+    "location": "Foreign",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about $5,400 a month from my US contracting work"
+  }
+]
+Example 3 - Client: "My wife has some business income but I don't know the figure, and I had no capital gains this year." -&gt; [
+  {
+    "income_type": "business",
+    "source": "Wife's business",
+    "amount": "Yes",
+    "frequency": null,
+    "location": "India",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "My wife has some business income but I don't know the figure"
+  },
+  {
+    "income_type": "capital_gains",
+    "source": null,
+    "amount": "0",
+    "frequency": "annual",
+    "location": null,
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "I had no capital gains this year"
+  }
+]</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
@@ -1787,45 +2051,45 @@
       <c r="I27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>KEEP? (open decision 1)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>health_insurance_coverage_adequacy</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Is the health insurance coverage adequate for the Client? [Original: Health Insurance Coverage Adequacy]</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>tax_and_insurance</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>d777e644efe64cc1bbc31917a6a9d9e8</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="165" customHeight="1">
+    <row r="29" ht="420" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1848,7 +2112,91 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all insurance policies (life term, health, ULIP, other). Each item is one policy with cover, premium and source. The two boolean adequacy judgements stay as separate attributes (open decision 1). Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every insurance policy the Client mentions into a single list so cover gaps can be assessed. The two boolean adequacy judgements (term_insurance_coverage_adequacy, health_insurance_coverage_adequacy) stay as separate attributes. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- insurance_type (enum, required): Type of policy, e.g. 'life_term', 'health'. Allowed values: life_term, health, ulip, other. Meanings: life_term = pure protection term cover; health = medical cover; ulip = Unit Linked Insurance Plan (investment-cum-insurance); other = any policy not listed.
+- insurer (string, nullable): Insurance company, e.g. 'HDFC Life', 'Star Health'.
+- policy_name (string, nullable): Plan name if given, e.g. 'Click 2 Protect'.
+- covered_members (string, nullable): Who is covered, e.g. 'self', 'self, spouse, 2 children'.
+- cover_amount (string, nullable): Sum assured / cover, e.g. 'INR 10000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- premium_amount (string, nullable): Premium per period, e.g. 'INR 12000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- premium_frequency (enum, nullable): How often the premium is paid, e.g. 'annual'. Allowed values: monthly, quarterly, annual, one_time.
+- source (enum, nullable): Who provides the cover, e.g. 'personal'. employer = group / corporate cover. Allowed values: employer, personal.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "I have a 1 crore HDFC term plan with 12k annual premium, and a 10 lakh Star Health family floater." -&gt; [
+  {
+    "insurance_type": "life_term",
+    "insurer": "HDFC Life",
+    "policy_name": null,
+    "covered_members": "self",
+    "cover_amount": "INR 10000000",
+    "premium_amount": "INR 12000",
+    "premium_frequency": "annual",
+    "source": "personal",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "1 crore HDFC term plan with 12k annual premium"
+  },
+  {
+    "insurance_type": "health",
+    "insurer": "Star Health",
+    "policy_name": null,
+    "covered_members": "family",
+    "cover_amount": "INR 1000000",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": "personal",
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "a 10 lakh Star Health family floater"
+  }
+]
+Example 2 - Client: "My employer gives me a 5 lakh health cover for my family; I pay nothing for it." -&gt; [
+  {
+    "insurance_type": "health",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": "family",
+    "cover_amount": "INR 500000",
+    "premium_amount": "0",
+    "premium_frequency": null,
+    "source": "employer",
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "My employer gives me a 5 lakh health cover for my family"
+  }
+]
+Example 3 - Client: "I do have a ULIP from years ago but I don't remember the cover, and I have no separate term cover of my own." -&gt; [
+  {
+    "insurance_type": "ulip",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": null,
+    "cover_amount": "Yes",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": "personal",
+    "confidence": 0.75,
+    "confidence_type": "quoted",
+    "evidence": "I do have a ULIP from years ago but I don't remember the cover"
+  },
+  {
+    "insurance_type": "life_term",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": null,
+    "cover_amount": "0",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": null,
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "I have no separate term cover of my own"
+  }
+]</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -1875,39 +2223,39 @@
       <c r="I29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>KEEP? (open decision 1)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>term_insurance_coverage_adequacy</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Is the term insurance coverage adequate for the Client? [Original: Term Insurance Coverage Adequacy]</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>tax_and_insurance</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>bfdf02a1739c4d4082b50228e4b3a749</t>
         </is>
@@ -2045,7 +2393,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="135" customHeight="1">
+    <row r="34" ht="420" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2068,7 +2416,79 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consolidated list of all liabilities/loans. Each item is one loan with lender, outstanding, EMI, rate and end year. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
+          <t>This attribute consolidates every liability or loan the Client mentions into a single list so outstanding debt and EMI load can be totalled. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed. Return the list directly - there is no outer value/confidence wrapper.
+Properties:
+- liability_type (enum, required): Type of loan, e.g. 'home_loan', 'credit_card_debt'. Allowed values: home_loan, vehicle_loan, education_loan, personal_loan, gold_loan, credit_card_debt, other_loan, total. Meanings: credit_card_debt = unpaid card dues; other_loan = any loan not listed; total = an explicitly stated total for the group.
+- lender (string, nullable): Lender name, e.g. 'SBI', 'HDFC Bank'.
+- outstanding_amount (string, nullable): Amount still owed, e.g. 'INR 4500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- emi_amount (string, nullable): Monthly EMI, e.g. 'INR 42000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.
+- interest_rate (string, nullable): Rate as stated, e.g. '8.5%'.
+- end_year (integer, nullable): Year the loan ends, e.g. 2040.
+- confidence (number, required): How confident the model is in this item (0-1).
+- confidence_type (enum, required): quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type. Allowed values: quoted, normalized, inferred, calculated, not_found.
+- evidence (string, nullable): Short verbatim quote(s) from the transcript supporting this item.
+Examples:
+Example 1 - Client: "I have an SBI home loan of 45 lakh outstanding, EMI of 42 thousand at 8.5%, till 2040." -&gt; [
+  {
+    "liability_type": "home_loan",
+    "lender": "SBI",
+    "outstanding_amount": "INR 4500000",
+    "emi_amount": "INR 42000",
+    "interest_rate": "8.5%",
+    "end_year": 2040,
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "SBI home loan of 45 lakh outstanding, EMI of 42 thousand at 8.5%, till 2040"
+  }
+]
+Example 2 - Client: "I have a 3 lakh personal loan and about 50 thousand outstanding on my credit card." -&gt; [
+  {
+    "liability_type": "personal_loan",
+    "lender": null,
+    "outstanding_amount": "INR 300000",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I have a 3 lakh personal loan"
+  },
+  {
+    "liability_type": "credit_card_debt",
+    "lender": null,
+    "outstanding_amount": "INR 50000",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "about 50 thousand outstanding on my credit card"
+  }
+]
+Example 3 - Client: "I still have some education loan left but I'm not sure how much, and I have no vehicle loan." -&gt; [
+  {
+    "liability_type": "education_loan",
+    "lender": null,
+    "outstanding_amount": "Yes",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I still have some education loan left but I'm not sure how much"
+  },
+  {
+    "liability_type": "vehicle_loan",
+    "lender": null,
+    "outstanding_amount": "0",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I have no vehicle loan"
+  }
+]</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
@@ -2375,54 +2795,336 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="120" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Consolidated list of all tax and compliance items (India / non-India filing, advance tax, TDS, GST, W-8BEN). Each item is one type with status, country, years and summary. Merges groups 'Tax' and 'Tax / Compliance'. Return one item per distinct holding/instance mentioned. If the Client mentions a type only in aggregate, return one item for that type. Return an empty list when the group is not discussed.</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>tax_type: enum [tax_filing_india | tax_filing_non_india | advance_tax | rental_tds | gst_services | w8_ben] (required)
-status: enum [Filed | Not Filed | Recommended | Not Needed | NRI Landlord | Resident Landlord | Client has GST | Requires GST | May need in future] (nullable)
-country: string (nullable)
-years: array (required)
-summary: string (nullable)
-confidence: number (required)
-confidence_type: enum [quoted | normalized | inferred | calculated | not_found] (required)
-evidence: string (nullable)</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>advance_tax</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Whether advance tax is recommended or not needed. [Original: Advance Tax]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Recommended | Not Needed</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>tax_and_insurance</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>f6a399cc2ca34baf9f764401ae10a46e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>rental_tds</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Relevant rental TDS classification. [Original: Rental TDS]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>NRI Landlord | Resident Landlord</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>88f8abe6a755483ab17801a7850f9e59</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>tax_filing_history_for_india</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Short summary of the Client's Indian tax filing history. [Original: Tax Filing History (For India)]</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>9789ab0a6df54a728f66abcb396d79cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>tax_filing_history_for_non_india</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Short summary of the Client's non-India tax filing history. [Original: Tax Filing History (For Non-India)]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>17f328237f7e4f2baf232828187a5eff</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>tax_filing_years_for_india</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Financial years for which Indian tax filing was explicitly mentioned. [Original: Tax Filing Years (For India)]</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>9a8b7c5cb4df45b88d432eb1f4bde6f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>tax_filing_years_for_non_india</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Years for which non-India tax filing was explicitly mentioned. [Original: Tax Filing Years (For Non-India)]</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>1300beb350504247b3d6880fd79f942b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Tax / Compliance</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>gst_services</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>GST requirement/status. [Original: GST services]</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Client has GST | Requires GST | May need in future</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>621a1e3e7ec442eeb76c3577fcdc18a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Tax / Compliance</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>w8_ben</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Status of W-8BEN filing. [Original: W8-BEN]</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Filed | Not Filed</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>tax_and_insurance</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>164400e20d5b40859440936b7e1de333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:I49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2433,14 +3135,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2471,7 +3173,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>assets  (Group: Assets - Agent: asset - Type: array of objects)</t>
         </is>
@@ -2502,7 +3204,11 @@
           <t>stocks | unlisted_stocks | equity_mutual_fund | equity_etf | commodity_etf | debt_etf | deposit | cash | debt_mf | personal_debt | bonds | reits | real_estate | crypto | others | total</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Type of asset holding, e.g. 'stocks', 'bonds', 'real_estate'.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2523,7 +3229,7 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Instrument / scheme / property / borrower name, e.g. 'HDFC Flexi Cap', 'Flat in Pune'</t>
+          <t>Instrument / scheme / property / borrower name, e.g. 'HDFC Flexi Cap', 'Flat in Whitefield, Bengaluru'.</t>
         </is>
       </c>
     </row>
@@ -2550,7 +3256,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Where the asset is held; for asset_type total, null = overall total</t>
+          <t>Where the asset is held, e.g. 'India'. For asset_type total, null = overall total across locations.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +3279,7 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Current value, or units held. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+          <t>Current value, or units held, e.g. 'INR 500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
@@ -2650,10 +3356,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1">
+    <row r="10" ht="150" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>Example 1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -2661,114 +3367,148 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>{
-  "asset_type": "bonds",
-  "name": "RBI Floating Rate Bond",
-  "location": "India",
-  "amount": "INR 500000",
-  "confidence": 0.9,
-  "confidence_type": "normalized",
-  "evidence": "I have about 5 lakh in RBI bonds"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+          <t>Client: "I have about 5 lakh in RBI bonds and around 2 lakh in HDFC Flexi Cap."
+-&gt;
+[
+  {
+    "asset_type": "bonds",
+    "name": "RBI bonds",
+    "location": "India",
+    "amount": "INR 500000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I have about 5 lakh in RBI bonds"
+  },
+  {
+    "asset_type": "equity_mutual_fund",
+    "name": "HDFC Flexi Cap",
+    "location": "India",
+    "amount": "INR 200000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "around 2 lakh in HDFC Flexi Cap"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I hold about $5,400 of Apple shares in my US brokerage."
+-&gt;
+[
+  {
+    "asset_type": "stocks",
+    "name": "Apple shares",
+    "location": "Foreign",
+    "amount": "USD 5400",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I hold about $5,400 of Apple shares in my US brokerage"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I do hold some crypto but I don't track the value, and I own no real estate."
+-&gt;
+[
+  {
+    "asset_type": "crypto",
+    "name": null,
+    "location": null,
+    "amount": "Yes",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I do hold some crypto but I don't track the value"
+  },
+  {
+    "asset_type": "real_estate",
+    "name": null,
+    "location": null,
+    "amount": "0",
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I own no real estate"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>accounts  (Group: Banking / Accounts - Agent: account - Type: array of objects)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>account_type</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>investment_account | bank_account | ppf | bank_deposit | nps | ssy | epf | pms | aif | crypto_broker | self_custody | others</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Bank / broker / fund house / wallet name, e.g. 'HDFC Bank', 'Zerodha'</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>account_name</t>
+          <t>account_type</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>investment_account | bank_account | ppf | bank_deposit | nps | ssy | epf | pms | aif | crypto_broker | self_custody | others</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Specific account or product name if given</t>
+          <t>Type of account, e.g. 'bank_account', 'ppf'.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2776,17 +3516,17 @@
           <t>nullable</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>India | Foreign</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Bank / broker / fund house / wallet name, e.g. 'HDFC Bank', 'Zerodha'.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>account_name</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2802,226 +3542,264 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+          <t>Specific account or product name if given, e.g. 'Salary account'.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>India | Foreign</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>How confident the model is in this item (0-1).</t>
+          <t>Where the account is held, e.g. 'India'.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>confidence_type</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+          <t>Account balance, e.g. 'INR 250000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
+          <t>required</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>How confident the model is in this item (0-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>confidence_type</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>Short verbatim quote(s) from the transcript supporting this item.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="110" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>{
-  "account_type": "bank_account",
-  "provider": "HDFC Bank",
-  "account_name": "Salary account",
-  "location": "India",
-  "balance": "INR 250000",
-  "confidence": 0.95,
-  "confidence_type": "quoted",
-  "evidence": "I have around 2.5 lakh in my HDFC salary account"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I have around 2.5 lakh in my HDFC salary account and about 8 lakh in PPF."
+-&gt;
+[
+  {
+    "account_type": "bank_account",
+    "provider": "HDFC Bank",
+    "account_name": "Salary account",
+    "location": "India",
+    "balance": "INR 250000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "around 2.5 lakh in my HDFC salary account"
+  },
+  {
+    "account_type": "ppf",
+    "provider": null,
+    "account_name": null,
+    "location": "India",
+    "balance": "INR 800000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about 8 lakh in PPF"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I keep about ten thousand dollars in my Chase savings account in the US."
+-&gt;
+[
+  {
+    "account_type": "bank_account",
+    "provider": "Chase",
+    "account_name": "Savings account",
+    "location": "Foreign",
+    "balance": "USD 10000",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about ten thousand dollars in my Chase savings account in the US"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I do have an NPS account but I don't remember the balance, and I have no crypto account."
+-&gt;
+[
+  {
+    "account_type": "nps",
+    "provider": null,
+    "account_name": null,
+    "location": "India",
+    "balance": "Yes",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I do have an NPS account but I don't remember the balance"
+  },
+  {
+    "account_type": "crypto_broker",
+    "provider": null,
+    "account_name": null,
+    "location": null,
+    "balance": "0",
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I have no crypto account"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>expenses  (Group: Expenses - Agent: expense - Type: array of objects)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>expense_type</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>rent | utilities | groceries | household_staff | childcare_school_fees | entertainment_dining | transport_fuel | family_support | shopping_purchases | subscriptions_memberships | insurance_premiums | travel_vacations | medical_expenses | loan_emis_education | loan_emis_personal | loan_emis_home | loan_emis_vehicle | loan_emis_others | loan_emis_total | charity_donations | miscellaneous | total</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>monthly | annual | one_time</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>As stated by the Client - do NOT convert annual to monthly</t>
-        </is>
-      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>expense_type</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3029,44 +3807,44 @@
           <t>required</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>rent | utilities | groceries | household_staff | childcare_school_fees | entertainment_dining | transport_fuel | family_support | shopping_purchases | subscriptions_memberships | insurance_premiums | travel_vacations | medical_expenses | loan_emis_education | loan_emis_personal | loan_emis_home | loan_emis_vehicle | loan_emis_others | loan_emis_total | charity_donations | miscellaneous | total</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>How confident the model is in this item (0-1).</t>
+          <t>Type of expense, e.g. 'rent', 'travel_vacations'.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>confidence_type</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+          <t>What the expense is for, e.g. '2BHK in Whitefield, Bengaluru'.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3082,193 +3860,231 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="110" customHeight="1">
+          <t>Amount per period, e.g. 'INR 30000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>monthly | annual | one_time</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>{
-  "expense_type": "rent",
-  "description": "2BHK in Whitefield, Bengaluru",
-  "amount": "INR 30000",
-  "frequency": "monthly",
-  "confidence": 0.95,
-  "confidence_type": "quoted",
-  "evidence": "We pay 30k rent for our 2BHK in Whitefield"
-}</t>
+          <t>How often it recurs, e.g. 'monthly'. Keep the Client's own period - do NOT convert annual to monthly.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>How confident the model is in this item (0-1).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>goals  (Group: Goals - Agent: goal - Type: array of objects)</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>confidence_type</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>goal_type</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>planning_a_child | child_s_college_education | child_s_higher_education | buying_a_house_india | buying_a_vehicle | wedding_expenses | parents_healthcare_fund | vacation_travel_fund | legacy_inheritance | financial_freedom_fire | other_goals</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="150" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Client: "We pay 30k rent for our 2BHK in Whitefield and 5k for utilities every month."
+-&gt;
+[
+  {
+    "expense_type": "rent",
+    "description": "2BHK in Whitefield, Bengaluru",
+    "amount": "INR 30000",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "We pay 30k rent for our 2BHK in Whitefield"
+  },
+  {
+    "expense_type": "utilities",
+    "description": null,
+    "amount": "INR 5000",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "5k for utilities every month"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="150" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>target_amount</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Target corpus / cost. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+          <t>Client: "We spend about 2 lakh a year on travel and vacations."
+-&gt;
+[
+  {
+    "expense_type": "travel_vacations",
+    "description": null,
+    "amount": "INR 200000",
+    "frequency": "annual",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about 2 lakh a year on travel and vacations"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="150" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>target_year</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Calendar year the Client wants to achieve the goal, e.g. 2032. If stated as 'in N years', add N to the meeting year and use confidence_type calculated</t>
+          <t>Client: "Groceries I don't track exactly, and we pay zero rent since we own the house."
+-&gt;
+[
+  {
+    "expense_type": "groceries",
+    "description": null,
+    "amount": "Yes",
+    "frequency": null,
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "Groceries I don't track exactly"
+  },
+  {
+    "expense_type": "rent",
+    "description": "Own house, no rent",
+    "amount": "0",
+    "frequency": "monthly",
+    "confidence": 0.9,
+    "confidence_type": "inferred",
+    "evidence": "we pay zero rent since we own the house"
+  }
+]</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>high | medium | low</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Only when the Client indicates it</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>How confident the model is in this item (0-1).</t>
-        </is>
-      </c>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>goals  (Group: Goals - Agent: goal - Type: array of objects)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>confidence_type</t>
+          <t>goal_type</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3283,19 +4099,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
+          <t>planning_a_child | child_s_college_education | child_s_higher_education | buying_a_house_india | buying_a_vehicle | wedding_expenses | parents_healthcare_fund | vacation_travel_fund | legacy_inheritance | financial_freedom_fire | other_goals</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+          <t>Type of goal, e.g. 'buying_a_house_india', 'financial_freedom_fire'.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3311,61 +4127,92 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="110" customHeight="1">
+          <t>Goal in the Client's own terms, e.g. "Daughter's MS in the US".</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>target_amount</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>{
-  "goal_type": "child_s_higher_education",
-  "description": "Daughter's MS in the US",
-  "target_amount": "INR 8000000",
-  "target_year": 2032,
-  "priority": "high",
-  "confidence": 0.85,
-  "confidence_type": "inferred",
-  "evidence": "We want to save around 80 lakh for our daughter's MS, maybe by 2032"
-}</t>
+          <t>Target corpus / cost, e.g. 'INR 8000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>target_year</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Calendar year the Client wants to achieve the goal, e.g. 2032. If stated as 'in N years', add N to the meeting year and use confidence_type calculated.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>income_sources  (Group: Income - Agent: income - Type: array of objects)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>high | medium | low</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>How important the goal is, e.g. 'high'. Only when the Client indicates it.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>income_type</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3373,40 +4220,44 @@
           <t>required</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>salary | business | capital_gains | rental | speculation | other_income</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>How confident the model is in this item (0-1).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>confidence_type</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Employer / business / property name</t>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3422,175 +4273,199 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="150" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>monthly | annual | one_time</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Client: "We want around 80 lakh for our daughter's MS in the US by 2032, and about 1 crore for a house in India."
+-&gt;
+[
+  {
+    "goal_type": "child_s_higher_education",
+    "description": "Daughter's MS in the US",
+    "target_amount": "INR 8000000",
+    "target_year": 2032,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "around 80 lakh for our daughter's MS in the US by 2032"
+  },
+  {
+    "goal_type": "buying_a_house_india",
+    "description": "House in India",
+    "target_amount": "INR 10000000",
+    "target_year": null,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "about 1 crore for a house in India"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="150" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>India | Foreign</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Client: "We want to retire in 15 years with a 5 crore corpus. (Meeting year 2026.)"
+-&gt;
+[
+  {
+    "goal_type": "financial_freedom_fire",
+    "description": "Retire with a 5 crore corpus",
+    "target_amount": "INR 50000000",
+    "target_year": 2041,
+    "priority": null,
+    "confidence": 0.8,
+    "confidence_type": "calculated",
+    "evidence": "retire in 15 years with a 5 crore corpus"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="150" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>How confident the model is in this item (0-1).</t>
+          <t>Client: "We are planning for a child but haven't fixed any amount yet."
+-&gt;
+[
+  {
+    "goal_type": "planning_a_child",
+    "description": "Planning for a child",
+    "target_amount": "Yes",
+    "target_year": null,
+    "priority": null,
+    "confidence": 0.85,
+    "confidence_type": "quoted",
+    "evidence": "planning for a child but haven't fixed any amount yet"
+  }
+]</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>confidence_type</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>income_sources  (Group: Income - Agent: income - Type: array of objects)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>income_type</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>salary | business | capital_gains | rental | speculation | other_income</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Type of income, e.g. 'salary', 'rental'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="110" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>{
-  "income_type": "salary",
-  "source": "Infosys",
-  "amount": "INR 200000",
-  "frequency": "monthly",
-  "location": "India",
-  "confidence": 0.95,
-  "confidence_type": "quoted",
-  "evidence": "My monthly salary at Infosys is 2 lakh"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Employer / business / property name, e.g. 'Infosys', 'Pune flat rent'.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>insurance_policies  (Group: Insurance - Agent: tax_and_insurance - Type: array of objects)</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Amount per period, e.g. 'INR 200000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>insurance_type</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3600,25 +4475,29 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>nullable</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>life_term | health | ulip | other</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+          <t>monthly | annual | one_time</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Pay frequency, e.g. 'monthly'.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>insurer</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3626,55 +4505,71 @@
           <t>nullable</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>India | Foreign</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Where the income is earned, e.g. 'India'.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>policy_name</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
+          <t>required</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>How confident the model is in this item (0-1).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>covered_members</t>
+          <t>confidence_type</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Who is covered, e.g. 'self, spouse, 2 children'</t>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>cover_amount</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3690,228 +4585,255 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sum assured / cover. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="150" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>premium_amount</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+          <t>Client: "My monthly salary at Infosys is 2 lakh and we get 25k rent from our Pune flat."
+-&gt;
+[
+  {
+    "income_type": "salary",
+    "source": "Infosys",
+    "amount": "INR 200000",
+    "frequency": "monthly",
+    "location": "India",
+    "confidence": 0.95,
+    "confidence_type": "normalized",
+    "evidence": "My monthly salary at Infosys is 2 lakh"
+  },
+  {
+    "income_type": "rental",
+    "source": "Pune flat",
+    "amount": "INR 25000",
+    "frequency": "monthly",
+    "location": "India",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "we get 25k rent from our Pune flat"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="150" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>premium_frequency</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>monthly | quarterly | annual | one_time</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I earn about $5,400 a month from my US contracting work."
+-&gt;
+[
+  {
+    "income_type": "salary",
+    "source": "US contracting work",
+    "amount": "USD 5400",
+    "frequency": "monthly",
+    "location": "Foreign",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "about $5,400 a month from my US contracting work"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="150" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>employer | personal</t>
-        </is>
-      </c>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>employer = group / corporate cover</t>
+          <t>Client: "My wife has some business income but I don't know the figure, and I had no capital gains this year."
+-&gt;
+[
+  {
+    "income_type": "business",
+    "source": "Wife's business",
+    "amount": "Yes",
+    "frequency": null,
+    "location": "India",
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "My wife has some business income but I don't know the figure"
+  },
+  {
+    "income_type": "capital_gains",
+    "source": null,
+    "amount": "0",
+    "frequency": "annual",
+    "location": null,
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "I had no capital gains this year"
+  }
+]</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>How confident the model is in this item (0-1).</t>
-        </is>
-      </c>
+      <c r="E64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>confidence_type</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
-        </is>
-      </c>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>insurance_policies  (Group: Insurance - Agent: tax_and_insurance - Type: array of objects)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>insurance_type</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>life_term | health | ulip | other</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Type of policy, e.g. 'life_term', 'health'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="110" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>{
-  "insurance_type": "life_term",
-  "insurer": "HDFC Life",
-  "policy_name": "Click 2 Protect",
-  "covered_members": "self",
-  "cover_amount": "INR 10000000",
-  "premium_amount": "INR 12000",
-  "premium_frequency": "annual",
-  "source": "personal",
-  "confidence": 0.9,
-  "confidence_type": "quoted",
-  "evidence": "I have a 1 crore HDFC term plan with 12k annual premium"
-}</t>
+          <t>Insurance company, e.g. 'HDFC Life', 'Star Health'.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>policy_name</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Plan name if given, e.g. 'Click 2 Protect'.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>liabilities  (Group: Liabilities - Agent: liability - Type: array of objects)</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>covered_members</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Who is covered, e.g. 'self', 'self, spouse, 2 children'.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>liability_type</t>
+          <t>cover_amount</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>home_loan | vehicle_loan | education_loan | personal_loan | gold_loan | credit_card_debt | other_loan | total</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Sum assured / cover, e.g. 'INR 10000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>lender</t>
+          <t>premium_amount</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3925,17 +4847,21 @@
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Premium per period, e.g. 'INR 12000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>outstanding_amount</t>
+          <t>premium_frequency</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3943,22 +4869,26 @@
           <t>nullable</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>monthly | quarterly | annual | one_time</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+          <t>How often the premium is paid, e.g. 'annual'.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>emi_amount</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3966,136 +4896,169 @@
           <t>nullable</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>employer | personal</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Monthly EMI. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
+          <t>Who provides the cover, e.g. 'personal'. employer = group / corporate cover.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>interest_rate</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
+          <t>required</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>e.g. '8.5%'</t>
+          <t>How confident the model is in this item (0-1).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>end_year</t>
+          <t>confidence_type</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Year the loan ends</t>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>nullable</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>How confident the model is in this item (0-1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="150" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>confidence_type</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+          <t>Client: "I have a 1 crore HDFC term plan with 12k annual premium, and a 10 lakh Star Health family floater."
+-&gt;
+[
+  {
+    "insurance_type": "life_term",
+    "insurer": "HDFC Life",
+    "policy_name": null,
+    "covered_members": "self",
+    "cover_amount": "INR 10000000",
+    "premium_amount": "INR 12000",
+    "premium_frequency": "annual",
+    "source": "personal",
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "1 crore HDFC term plan with 12k annual premium"
+  },
+  {
+    "insurance_type": "health",
+    "insurer": "Star Health",
+    "policy_name": null,
+    "covered_members": "family",
+    "cover_amount": "INR 1000000",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": "personal",
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "a 10 lakh Star Health family floater"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="150" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="110" customHeight="1">
+          <t>Client: "My employer gives me a 5 lakh health cover for my family; I pay nothing for it."
+-&gt;
+[
+  {
+    "insurance_type": "health",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": "family",
+    "cover_amount": "INR 500000",
+    "premium_amount": "0",
+    "premium_frequency": null,
+    "source": "employer",
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "My employer gives me a 5 lakh health cover for my family"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="150" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>Example 3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
@@ -4103,17 +5066,36 @@
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>{
-  "liability_type": "home_loan",
-  "lender": "SBI",
-  "outstanding_amount": "INR 4500000",
-  "emi_amount": "INR 42000",
-  "interest_rate": "8.5%",
-  "end_year": 2040,
-  "confidence": 0.9,
-  "confidence_type": "normalized",
-  "evidence": "SBI home loan of 45 lakh, EMI 42 thousand at 8.5%, till 2040"
-}</t>
+          <t>Client: "I do have a ULIP from years ago but I don't remember the cover, and I have no separate term cover of my own."
+-&gt;
+[
+  {
+    "insurance_type": "ulip",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": null,
+    "cover_amount": "Yes",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": "personal",
+    "confidence": 0.75,
+    "confidence_type": "quoted",
+    "evidence": "I do have a ULIP from years ago but I don't remember the cover"
+  },
+  {
+    "insurance_type": "life_term",
+    "insurer": null,
+    "policy_name": null,
+    "covered_members": null,
+    "cover_amount": "0",
+    "premium_amount": null,
+    "premium_frequency": null,
+    "source": null,
+    "confidence": 0.9,
+    "confidence_type": "quoted",
+    "evidence": "I have no separate term cover of my own"
+  }
+]</t>
         </is>
       </c>
     </row>
@@ -4125,9 +5107,9 @@
       <c r="E80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>tax_items  (Group: Tax - Agent: tax_and_insurance - Type: array of objects)</t>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>liabilities  (Group: Liabilities - Agent: liability - Type: array of objects)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n"/>
@@ -4138,7 +5120,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>tax_type</t>
+          <t>liability_type</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4153,20 +5135,24 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>tax_filing_india | tax_filing_non_india | advance_tax | rental_tds | gst_services | w8_ben</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>home_loan | vehicle_loan | education_loan | personal_loan | gold_loan | credit_card_debt | other_loan | total</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Type of loan, e.g. 'home_loan', 'credit_card_debt'.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>lender</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4174,21 +5160,17 @@
           <t>nullable</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Filed | Not Filed | Recommended | Not Needed | NRI Landlord | Resident Landlord | Client has GST | Requires GST | May need in future</t>
-        </is>
-      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Allowed per tax_type - tax_filing_*: Filed / Not Filed; advance_tax: Recommended / Not Needed; rental_tds: NRI Landlord / Resident Landlord; gst_services: Client has GST / Requires GST / May need in future; w8_ben: Filed / Not Filed</t>
+          <t>Lender name, e.g. 'SBI', 'HDFC Bank'.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>outstanding_amount</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4204,37 +5186,37 @@
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>For tax_filing_non_india: the country</t>
+          <t>Amount still owed, e.g. 'INR 4500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>emi_amount</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>nullable</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Financial / tax years mentioned, e.g. 'FY2024-25' for India, '2024' elsewhere</t>
+          <t>Monthly EMI, e.g. 'INR 42000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>interest_rate</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4250,42 +5232,42 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>One-line summary of what the Client said</t>
+          <t>Rate as stated, e.g. '8.5%'.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>end_year</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>nullable</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>How confident the model is in this item (0-1).</t>
+          <t>Year the loan ends, e.g. 2040.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>confidence_type</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4293,84 +5275,189 @@
           <t>required</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>quoted | normalized | inferred | calculated | not_found</t>
-        </is>
-      </c>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+          <t>How confident the model is in this item (0-1).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>confidence_type</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>quoted | normalized | inferred | calculated | not_found</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="110" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>{
-  "tax_type": "tax_filing_india",
-  "status": "Filed",
-  "country": null,
-  "years": [
-    "FY2024-25"
-  ],
-  "summary": "Filed India return for FY24-25",
-  "confidence": 0.95,
-  "confidence_type": "quoted",
-  "evidence": "We filed our India taxes for FY24-25 in July"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+          <t>Short verbatim quote(s) from the transcript supporting this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="150" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Example 1</t>
+        </is>
+      </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I have an SBI home loan of 45 lakh outstanding, EMI of 42 thousand at 8.5%, till 2040."
+-&gt;
+[
+  {
+    "liability_type": "home_loan",
+    "lender": "SBI",
+    "outstanding_amount": "INR 4500000",
+    "emi_amount": "INR 42000",
+    "interest_rate": "8.5%",
+    "end_year": 2040,
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "SBI home loan of 45 lakh outstanding, EMI of 42 thousand at 8.5%, till 2040"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="150" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I have a 3 lakh personal loan and about 50 thousand outstanding on my credit card."
+-&gt;
+[
+  {
+    "liability_type": "personal_loan",
+    "lender": null,
+    "outstanding_amount": "INR 300000",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.9,
+    "confidence_type": "normalized",
+    "evidence": "I have a 3 lakh personal loan"
+  },
+  {
+    "liability_type": "credit_card_debt",
+    "lender": null,
+    "outstanding_amount": "INR 50000",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.85,
+    "confidence_type": "normalized",
+    "evidence": "about 50 thousand outstanding on my credit card"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="150" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Client: "I still have some education loan left but I'm not sure how much, and I have no vehicle loan."
+-&gt;
+[
+  {
+    "liability_type": "education_loan",
+    "lender": null,
+    "outstanding_amount": "Yes",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.8,
+    "confidence_type": "quoted",
+    "evidence": "I still have some education loan left but I'm not sure how much"
+  },
+  {
+    "liability_type": "vehicle_loan",
+    "lender": null,
+    "outstanding_amount": "0",
+    "emi_amount": null,
+    "interest_rate": null,
+    "end_year": null,
+    "confidence": 0.95,
+    "confidence_type": "quoted",
+    "evidence": "I have no vehicle loan"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <mergeCells count="8">
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A69:E69"/>
+  <mergeCells count="7">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4382,7 +5469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6892,17 +7979,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>advance_tax</t>
+          <t>health_insurance_coverage_adequacy</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6912,29 +7999,25 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=advance_tax</t>
-        </is>
-      </c>
+          <t>kept as-is</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>rental_tds</t>
+          <t>term_insurance_coverage_adequacy</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6944,265 +8027,13 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=rental_tds</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>tax_filing_history_for_india</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=tax_filing_india (summary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>tax_filing_history_for_non_india</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=tax_filing_non_india (summary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>tax_filing_years_for_india</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=tax_filing_india (years)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>tax_filing_years_for_non_india</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=tax_filing_non_india (years)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Tax / Compliance</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>gst_services</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=gst_services</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Tax / Compliance</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>w8_ben</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>tax_type=w8_ben</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>health_insurance_coverage_adequacy</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>kept as-is (open decision 1)</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>term_insurance_coverage_adequacy</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>tax_and_insurance</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>kept as-is (open decision 1)</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>kept as-is</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F88"/>
+  <autoFilter ref="A1:F80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7213,7 +8044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7233,7 +8064,7 @@
       </c>
     </row>
     <row r="2" ht="260" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>assets</t>
         </is>
@@ -7265,14 +8096,14 @@
           "others",
           "total"
         ],
-        "description": ""
+        "description": "Type of asset holding, e.g. 'stocks', 'bonds', 'real_estate'."
       },
       "name": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Instrument / scheme / property / borrower name, e.g. 'HDFC Flexi Cap', 'Flat in Pune'"
+        "description": "Instrument / scheme / property / borrower name, e.g. 'HDFC Flexi Cap', 'Flat in Whitefield, Bengaluru'."
       },
       "location": {
         "type": [
@@ -7284,14 +8115,14 @@
           "Foreign",
           null
         ],
-        "description": "Where the asset is held; for asset_type total, null = overall total"
+        "description": "Where the asset is held, e.g. 'India'. For asset_type total, null = overall total across locations."
       },
       "amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Current value, or units held. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Current value, or units held, e.g. 'INR 500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "confidence": {
         "type": "number",
@@ -7332,7 +8163,7 @@
       </c>
     </row>
     <row r="3" ht="260" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>accounts</t>
         </is>
@@ -7360,21 +8191,21 @@
           "self_custody",
           "others"
         ],
-        "description": ""
+        "description": "Type of account, e.g. 'bank_account', 'ppf'."
       },
       "provider": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Bank / broker / fund house / wallet name, e.g. 'HDFC Bank', 'Zerodha'"
+        "description": "Bank / broker / fund house / wallet name, e.g. 'HDFC Bank', 'Zerodha'."
       },
       "account_name": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Specific account or product name if given"
+        "description": "Specific account or product name if given, e.g. 'Salary account'."
       },
       "location": {
         "type": [
@@ -7386,14 +8217,14 @@
           "Foreign",
           null
         ],
-        "description": ""
+        "description": "Where the account is held, e.g. 'India'."
       },
       "balance": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Account balance, e.g. 'INR 250000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "confidence": {
         "type": "number",
@@ -7435,7 +8266,7 @@
       </c>
     </row>
     <row r="4" ht="260" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>expenses</t>
         </is>
@@ -7473,21 +8304,21 @@
           "miscellaneous",
           "total"
         ],
-        "description": ""
+        "description": "Type of expense, e.g. 'rent', 'travel_vacations'."
       },
       "description": {
         "type": [
           "string",
           "null"
         ],
-        "description": ""
+        "description": "What the expense is for, e.g. '2BHK in Whitefield, Bengaluru'."
       },
       "amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Amount per period, e.g. 'INR 30000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "frequency": {
         "type": [
@@ -7500,7 +8331,7 @@
           "one_time",
           null
         ],
-        "description": "As stated by the Client - do NOT convert annual to monthly"
+        "description": "How often it recurs, e.g. 'monthly'. Keep the Client's own period - do NOT convert annual to monthly."
       },
       "confidence": {
         "type": "number",
@@ -7541,7 +8372,7 @@
       </c>
     </row>
     <row r="5" ht="260" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>goals</t>
         </is>
@@ -7568,28 +8399,28 @@
           "financial_freedom_fire",
           "other_goals"
         ],
-        "description": ""
+        "description": "Type of goal, e.g. 'buying_a_house_india', 'financial_freedom_fire'."
       },
       "description": {
         "type": [
           "string",
           "null"
         ],
-        "description": ""
+        "description": "Goal in the Client's own terms, e.g. \"Daughter's MS in the US\"."
       },
       "target_amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Target corpus / cost. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Target corpus / cost, e.g. 'INR 8000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "target_year": {
         "type": [
           "integer",
           "null"
         ],
-        "description": "Calendar year the Client wants to achieve the goal, e.g. 2032. If stated as 'in N years', add N to the meeting year and use confidence_type calculated"
+        "description": "Calendar year the Client wants to achieve the goal, e.g. 2032. If stated as 'in N years', add N to the meeting year and use confidence_type calculated."
       },
       "priority": {
         "type": [
@@ -7602,7 +8433,7 @@
           "low",
           null
         ],
-        "description": "Only when the Client indicates it"
+        "description": "How important the goal is, e.g. 'high'. Only when the Client indicates it."
       },
       "confidence": {
         "type": "number",
@@ -7644,7 +8475,7 @@
       </c>
     </row>
     <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>income_sources</t>
         </is>
@@ -7666,21 +8497,21 @@
           "speculation",
           "other_income"
         ],
-        "description": ""
+        "description": "Type of income, e.g. 'salary', 'rental'."
       },
       "source": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Employer / business / property name"
+        "description": "Employer / business / property name, e.g. 'Infosys', 'Pune flat rent'."
       },
       "amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Amount per period, e.g. 'INR 200000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "frequency": {
         "type": [
@@ -7693,7 +8524,7 @@
           "one_time",
           null
         ],
-        "description": ""
+        "description": "Pay frequency, e.g. 'monthly'."
       },
       "location": {
         "type": [
@@ -7705,7 +8536,7 @@
           "Foreign",
           null
         ],
-        "description": ""
+        "description": "Where the income is earned, e.g. 'India'."
       },
       "confidence": {
         "type": "number",
@@ -7747,7 +8578,7 @@
       </c>
     </row>
     <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>insurance_policies</t>
         </is>
@@ -7767,42 +8598,42 @@
           "ulip",
           "other"
         ],
-        "description": ""
+        "description": "Type of policy, e.g. 'life_term', 'health'."
       },
       "insurer": {
         "type": [
           "string",
           "null"
         ],
-        "description": ""
+        "description": "Insurance company, e.g. 'HDFC Life', 'Star Health'."
       },
       "policy_name": {
         "type": [
           "string",
           "null"
         ],
-        "description": ""
+        "description": "Plan name if given, e.g. 'Click 2 Protect'."
       },
       "covered_members": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Who is covered, e.g. 'self, spouse, 2 children'"
+        "description": "Who is covered, e.g. 'self', 'self, spouse, 2 children'."
       },
       "cover_amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Sum assured / cover. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Sum assured / cover, e.g. 'INR 10000000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "premium_amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Premium per period, e.g. 'INR 12000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "premium_frequency": {
         "type": [
@@ -7816,7 +8647,7 @@
           "one_time",
           null
         ],
-        "description": ""
+        "description": "How often the premium is paid, e.g. 'annual'."
       },
       "source": {
         "type": [
@@ -7828,7 +8659,7 @@
           "personal",
           null
         ],
-        "description": "employer = group / corporate cover"
+        "description": "Who provides the cover, e.g. 'personal'. employer = group / corporate cover."
       },
       "confidence": {
         "type": "number",
@@ -7873,7 +8704,7 @@
       </c>
     </row>
     <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>liabilities</t>
         </is>
@@ -7897,42 +8728,42 @@
           "other_loan",
           "total"
         ],
-        "description": ""
+        "description": "Type of loan, e.g. 'home_loan', 'credit_card_debt'."
       },
       "lender": {
         "type": [
           "string",
           "null"
         ],
-        "description": ""
+        "description": "Lender name, e.g. 'SBI', 'HDFC Bank'."
       },
       "outstanding_amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Amount still owed, e.g. 'INR 4500000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "emi_amount": {
         "type": [
           "string",
           "null"
         ],
-        "description": "Monthly EMI. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
+        "description": "Monthly EMI, e.g. 'INR 42000'. Currency code or unit, one space, digits only - no commas, no symbols, no words: 'INR 1000000', 'USD 5400', '50 units', '0.5 BTC'. Convert lakh/crore to digits (10 lakh -&gt; INR 1000000). '0' when the Client says they have none of this type. 'Yes' when the Client has it but gave no figure. null when not mentioned."
       },
       "interest_rate": {
         "type": [
           "string",
           "null"
         ],
-        "description": "e.g. '8.5%'"
+        "description": "Rate as stated, e.g. '8.5%'."
       },
       "end_year": {
         "type": [
           "integer",
           "null"
         ],
-        "description": "Year the loan ends"
+        "description": "Year the loan ends, e.g. 2040."
       },
       "confidence": {
         "type": "number",
@@ -7974,110 +8805,6 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="260" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>tax_items</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>{
-  "type": "array",
-  "items": {
-    "type": "object",
-    "properties": {
-      "tax_type": {
-        "type": "string",
-        "enum": [
-          "tax_filing_india",
-          "tax_filing_non_india",
-          "advance_tax",
-          "rental_tds",
-          "gst_services",
-          "w8_ben"
-        ],
-        "description": ""
-      },
-      "status": {
-        "type": [
-          "string",
-          "null"
-        ],
-        "enum": [
-          "Filed",
-          "Not Filed",
-          "Recommended",
-          "Not Needed",
-          "NRI Landlord",
-          "Resident Landlord",
-          "Client has GST",
-          "Requires GST",
-          "May need in future",
-          null
-        ],
-        "description": "Allowed per tax_type - tax_filing_*: Filed / Not Filed; advance_tax: Recommended / Not Needed; rental_tds: NRI Landlord / Resident Landlord; gst_services: Client has GST / Requires GST / May need in future; w8_ben: Filed / Not Filed"
-      },
-      "country": {
-        "type": [
-          "string",
-          "null"
-        ],
-        "description": "For tax_filing_non_india: the country"
-      },
-      "years": {
-        "type": "array",
-        "items": {
-          "type": "string"
-        },
-        "description": "Financial / tax years mentioned, e.g. 'FY2024-25' for India, '2024' elsewhere"
-      },
-      "summary": {
-        "type": [
-          "string",
-          "null"
-        ],
-        "description": "One-line summary of what the Client said"
-      },
-      "confidence": {
-        "type": "number",
-        "description": "How confident the model is in this item (0-1)."
-      },
-      "confidence_type": {
-        "type": "string",
-        "enum": [
-          "quoted",
-          "normalized",
-          "inferred",
-          "calculated",
-          "not_found"
-        ],
-        "description": "quoted = stated verbatim; normalized = stated but reformatted (e.g. '10 lakh' -&gt; 'INR 1000000'); inferred = clearly implied; calculated = derived from several stated pieces; not_found = no value found for this type."
-      },
-      "evidence": {
-        "type": [
-          "string",
-          "null"
-        ],
-        "description": "Short verbatim quote(s) from the transcript supporting this item."
-      }
-    },
-    "required": [
-      "tax_type",
-      "status",
-      "country",
-      "years",
-      "summary",
-      "confidence",
-      "confidence_type",
-      "evidence"
-    ],
-    "additionalProperties": false
-  }
-}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:B1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
